--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467570</v>
+        <v>120467583</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519395</v>
+        <v>519401</v>
       </c>
       <c r="R2" t="n">
-        <v>7034197</v>
+        <v>7034214</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467559</v>
+        <v>120467580</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519429</v>
+        <v>519388</v>
       </c>
       <c r="R3" t="n">
-        <v>7034461</v>
+        <v>7034221</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467588</v>
+        <v>120467582</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519413</v>
+        <v>519393</v>
       </c>
       <c r="R4" t="n">
-        <v>7034235</v>
+        <v>7034225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467556</v>
+        <v>120467626</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519458</v>
+        <v>519435</v>
       </c>
       <c r="R5" t="n">
-        <v>7034427</v>
+        <v>7034340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467595</v>
+        <v>120467573</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519487</v>
+        <v>519380</v>
       </c>
       <c r="R6" t="n">
-        <v>7034345</v>
+        <v>7034214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467568</v>
+        <v>120467594</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519370</v>
+        <v>519475</v>
       </c>
       <c r="R7" t="n">
-        <v>7034235</v>
+        <v>7034336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467557</v>
+        <v>120467555</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519397</v>
+        <v>519477</v>
       </c>
       <c r="R8" t="n">
-        <v>7034351</v>
+        <v>7034429</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467573</v>
+        <v>120467560</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519380</v>
+        <v>519436</v>
       </c>
       <c r="R9" t="n">
-        <v>7034214</v>
+        <v>7034470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467558</v>
+        <v>120467568</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519402</v>
+        <v>519370</v>
       </c>
       <c r="R10" t="n">
-        <v>7034350</v>
+        <v>7034235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467575</v>
+        <v>120467572</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1681,7 +1676,7 @@
         <v>519384</v>
       </c>
       <c r="R11" t="n">
-        <v>7034223</v>
+        <v>7034205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467569</v>
+        <v>120467561</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519355</v>
+        <v>519408</v>
       </c>
       <c r="R12" t="n">
-        <v>7034201</v>
+        <v>7034486</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467626</v>
+        <v>120467595</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519435</v>
+        <v>519487</v>
       </c>
       <c r="R13" t="n">
-        <v>7034340</v>
+        <v>7034345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467591</v>
+        <v>120467577</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519446</v>
+        <v>519386</v>
       </c>
       <c r="R14" t="n">
-        <v>7034304</v>
+        <v>7034229</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467564</v>
+        <v>120467559</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519376</v>
+        <v>519429</v>
       </c>
       <c r="R15" t="n">
-        <v>7034350</v>
+        <v>7034461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467566</v>
+        <v>120467553</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519393</v>
+        <v>519489</v>
       </c>
       <c r="R16" t="n">
-        <v>7034297</v>
+        <v>7034525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467584</v>
+        <v>120467579</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519403</v>
+        <v>519392</v>
       </c>
       <c r="R17" t="n">
-        <v>7034216</v>
+        <v>7034219</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467561</v>
+        <v>120467627</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519408</v>
+        <v>519361</v>
       </c>
       <c r="R18" t="n">
-        <v>7034486</v>
+        <v>7034385</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2458,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467593</v>
+        <v>120467588</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519467</v>
+        <v>519413</v>
       </c>
       <c r="R19" t="n">
-        <v>7034318</v>
+        <v>7034235</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467567</v>
+        <v>120467586</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2636,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519393</v>
+        <v>519422</v>
       </c>
       <c r="R20" t="n">
-        <v>7034245</v>
+        <v>7034236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467627</v>
+        <v>120467629</v>
       </c>
       <c r="B21" t="n">
         <v>90598</v>
@@ -2743,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519361</v>
+        <v>519509</v>
       </c>
       <c r="R21" t="n">
-        <v>7034385</v>
+        <v>7034395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467589</v>
+        <v>120467628</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519426</v>
+        <v>519399</v>
       </c>
       <c r="R22" t="n">
-        <v>7034284</v>
+        <v>7034196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,11 +2876,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467555</v>
+        <v>120467590</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519477</v>
+        <v>519424</v>
       </c>
       <c r="R23" t="n">
-        <v>7034429</v>
+        <v>7034288</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467592</v>
+        <v>120467596</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3059,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519472</v>
+        <v>519510</v>
       </c>
       <c r="R24" t="n">
-        <v>7034318</v>
+        <v>7034345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3089,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467580</v>
+        <v>120467589</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3166,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519388</v>
+        <v>519426</v>
       </c>
       <c r="R25" t="n">
-        <v>7034221</v>
+        <v>7034284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467560</v>
+        <v>120467592</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3273,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519436</v>
+        <v>519472</v>
       </c>
       <c r="R26" t="n">
-        <v>7034470</v>
+        <v>7034318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467565</v>
+        <v>120467597</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3380,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519363</v>
+        <v>519497</v>
       </c>
       <c r="R27" t="n">
-        <v>7034334</v>
+        <v>7034345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467572</v>
+        <v>120467570</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3487,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519384</v>
+        <v>519395</v>
       </c>
       <c r="R28" t="n">
-        <v>7034205</v>
+        <v>7034197</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467571</v>
+        <v>120467591</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3594,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519383</v>
+        <v>519446</v>
       </c>
       <c r="R29" t="n">
-        <v>7034199</v>
+        <v>7034304</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467590</v>
+        <v>120467598</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3701,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519424</v>
+        <v>519500</v>
       </c>
       <c r="R30" t="n">
-        <v>7034288</v>
+        <v>7034377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467582</v>
+        <v>120467556</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3808,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519393</v>
+        <v>519458</v>
       </c>
       <c r="R31" t="n">
-        <v>7034225</v>
+        <v>7034427</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3838,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,7 +3865,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467586</v>
+        <v>120467564</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3915,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519422</v>
+        <v>519376</v>
       </c>
       <c r="R32" t="n">
-        <v>7034236</v>
+        <v>7034350</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3945,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,7 +3972,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467587</v>
+        <v>120467574</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4022,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519412</v>
+        <v>519385</v>
       </c>
       <c r="R33" t="n">
-        <v>7034235</v>
+        <v>7034219</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4089,7 +4079,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467598</v>
+        <v>120467575</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4129,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519500</v>
+        <v>519384</v>
       </c>
       <c r="R34" t="n">
-        <v>7034377</v>
+        <v>7034223</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,7 +4186,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467574</v>
+        <v>120467565</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4236,10 +4226,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519385</v>
+        <v>519363</v>
       </c>
       <c r="R35" t="n">
-        <v>7034219</v>
+        <v>7034334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4266,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,7 +4293,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467553</v>
+        <v>120467587</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4343,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519489</v>
+        <v>519412</v>
       </c>
       <c r="R36" t="n">
-        <v>7034525</v>
+        <v>7034235</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4373,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,7 +4400,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467579</v>
+        <v>120467554</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4450,10 +4440,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519392</v>
+        <v>519486</v>
       </c>
       <c r="R37" t="n">
-        <v>7034219</v>
+        <v>7034475</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4517,7 +4507,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467583</v>
+        <v>120467571</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4557,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519401</v>
+        <v>519383</v>
       </c>
       <c r="R38" t="n">
-        <v>7034214</v>
+        <v>7034199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4587,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,7 +4614,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467596</v>
+        <v>120467581</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519510</v>
+        <v>519389</v>
       </c>
       <c r="R39" t="n">
-        <v>7034345</v>
+        <v>7034222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4694,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,7 +4721,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467577</v>
+        <v>120467566</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4771,10 +4761,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519386</v>
+        <v>519393</v>
       </c>
       <c r="R40" t="n">
-        <v>7034229</v>
+        <v>7034297</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4801,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4838,7 +4828,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467578</v>
+        <v>120467562</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4878,10 +4868,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519389</v>
+        <v>519399</v>
       </c>
       <c r="R41" t="n">
-        <v>7034229</v>
+        <v>7034481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4908,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,7 +4935,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467554</v>
+        <v>120467593</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4985,10 +4975,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519486</v>
+        <v>519467</v>
       </c>
       <c r="R42" t="n">
-        <v>7034475</v>
+        <v>7034318</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5015,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5052,10 +5042,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467628</v>
+        <v>120467584</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5068,21 +5058,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5092,10 +5082,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519399</v>
+        <v>519403</v>
       </c>
       <c r="R43" t="n">
-        <v>7034196</v>
+        <v>7034216</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5128,6 +5118,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5154,7 +5149,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467581</v>
+        <v>120467578</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5197,7 +5192,7 @@
         <v>519389</v>
       </c>
       <c r="R44" t="n">
-        <v>7034222</v>
+        <v>7034229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5234,7 +5229,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,7 +5256,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467597</v>
+        <v>120467576</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519497</v>
+        <v>519383</v>
       </c>
       <c r="R45" t="n">
-        <v>7034345</v>
+        <v>7034225</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5336,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,7 +5363,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467576</v>
+        <v>120467558</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5408,10 +5403,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519383</v>
+        <v>519402</v>
       </c>
       <c r="R46" t="n">
-        <v>7034225</v>
+        <v>7034350</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,10 +5470,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467629</v>
+        <v>120467569</v>
       </c>
       <c r="B47" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5491,21 +5486,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5515,10 +5510,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519509</v>
+        <v>519355</v>
       </c>
       <c r="R47" t="n">
-        <v>7034395</v>
+        <v>7034201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5551,6 +5546,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5577,7 +5577,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467562</v>
+        <v>120467557</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519399</v>
+        <v>519397</v>
       </c>
       <c r="R48" t="n">
-        <v>7034481</v>
+        <v>7034351</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467594</v>
+        <v>120467567</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519475</v>
+        <v>519393</v>
       </c>
       <c r="R49" t="n">
-        <v>7034336</v>
+        <v>7034245</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467583</v>
+        <v>120467574</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519401</v>
+        <v>519385</v>
       </c>
       <c r="R2" t="n">
-        <v>7034214</v>
+        <v>7034219</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467580</v>
+        <v>120467575</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519388</v>
+        <v>519384</v>
       </c>
       <c r="R3" t="n">
-        <v>7034221</v>
+        <v>7034223</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467582</v>
+        <v>120467553</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519393</v>
+        <v>519489</v>
       </c>
       <c r="R4" t="n">
-        <v>7034225</v>
+        <v>7034525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467626</v>
+        <v>120467584</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519435</v>
+        <v>519403</v>
       </c>
       <c r="R5" t="n">
-        <v>7034340</v>
+        <v>7034216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467573</v>
+        <v>120467629</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519380</v>
+        <v>519509</v>
       </c>
       <c r="R6" t="n">
-        <v>7034214</v>
+        <v>7034395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467594</v>
+        <v>120467582</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519475</v>
+        <v>519393</v>
       </c>
       <c r="R7" t="n">
-        <v>7034336</v>
+        <v>7034225</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467555</v>
+        <v>120467569</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519477</v>
+        <v>519355</v>
       </c>
       <c r="R8" t="n">
-        <v>7034429</v>
+        <v>7034201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467560</v>
+        <v>120467573</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519436</v>
+        <v>519380</v>
       </c>
       <c r="R9" t="n">
-        <v>7034470</v>
+        <v>7034214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467568</v>
+        <v>120467560</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519370</v>
+        <v>519436</v>
       </c>
       <c r="R10" t="n">
-        <v>7034235</v>
+        <v>7034470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467572</v>
+        <v>120467566</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519384</v>
+        <v>519393</v>
       </c>
       <c r="R11" t="n">
-        <v>7034205</v>
+        <v>7034297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467561</v>
+        <v>120467576</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519408</v>
+        <v>519383</v>
       </c>
       <c r="R12" t="n">
-        <v>7034486</v>
+        <v>7034225</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467595</v>
+        <v>120467558</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519487</v>
+        <v>519402</v>
       </c>
       <c r="R13" t="n">
-        <v>7034345</v>
+        <v>7034350</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467577</v>
+        <v>120467556</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519386</v>
+        <v>519458</v>
       </c>
       <c r="R14" t="n">
-        <v>7034229</v>
+        <v>7034427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467559</v>
+        <v>120467590</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519429</v>
+        <v>519424</v>
       </c>
       <c r="R15" t="n">
-        <v>7034461</v>
+        <v>7034288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467553</v>
+        <v>120467562</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519489</v>
+        <v>519399</v>
       </c>
       <c r="R16" t="n">
-        <v>7034525</v>
+        <v>7034481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467579</v>
+        <v>120467557</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519392</v>
+        <v>519397</v>
       </c>
       <c r="R17" t="n">
-        <v>7034219</v>
+        <v>7034351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467627</v>
+        <v>120467554</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519361</v>
+        <v>519486</v>
       </c>
       <c r="R18" t="n">
-        <v>7034385</v>
+        <v>7034475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467588</v>
+        <v>120467628</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519413</v>
+        <v>519399</v>
       </c>
       <c r="R19" t="n">
-        <v>7034235</v>
+        <v>7034196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2565,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467586</v>
+        <v>120467595</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519422</v>
+        <v>519487</v>
       </c>
       <c r="R20" t="n">
-        <v>7034236</v>
+        <v>7034345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467629</v>
+        <v>120467570</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519509</v>
+        <v>519395</v>
       </c>
       <c r="R21" t="n">
-        <v>7034395</v>
+        <v>7034197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2774,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467628</v>
+        <v>120467565</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519399</v>
+        <v>519363</v>
       </c>
       <c r="R22" t="n">
-        <v>7034196</v>
+        <v>7034334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,6 +2881,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467590</v>
+        <v>120467594</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2942,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519424</v>
+        <v>519475</v>
       </c>
       <c r="R23" t="n">
-        <v>7034288</v>
+        <v>7034336</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467596</v>
+        <v>120467564</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3049,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519510</v>
+        <v>519376</v>
       </c>
       <c r="R24" t="n">
-        <v>7034345</v>
+        <v>7034350</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467589</v>
+        <v>120467578</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3156,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519426</v>
+        <v>519389</v>
       </c>
       <c r="R25" t="n">
-        <v>7034284</v>
+        <v>7034229</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3206,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467592</v>
+        <v>120467587</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3263,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519472</v>
+        <v>519412</v>
       </c>
       <c r="R26" t="n">
-        <v>7034318</v>
+        <v>7034235</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3313,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467597</v>
+        <v>120467588</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3370,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519497</v>
+        <v>519413</v>
       </c>
       <c r="R27" t="n">
-        <v>7034345</v>
+        <v>7034235</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3420,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,7 +3447,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467570</v>
+        <v>120467591</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3477,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519395</v>
+        <v>519446</v>
       </c>
       <c r="R28" t="n">
-        <v>7034197</v>
+        <v>7034304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,7 +3554,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467591</v>
+        <v>120467596</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3584,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519446</v>
+        <v>519510</v>
       </c>
       <c r="R29" t="n">
-        <v>7034304</v>
+        <v>7034345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3634,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3661,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467598</v>
+        <v>120467581</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3691,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519500</v>
+        <v>519389</v>
       </c>
       <c r="R30" t="n">
-        <v>7034377</v>
+        <v>7034222</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467556</v>
+        <v>120467586</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3798,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519458</v>
+        <v>519422</v>
       </c>
       <c r="R31" t="n">
-        <v>7034427</v>
+        <v>7034236</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3848,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,7 +3875,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467564</v>
+        <v>120467561</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3905,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519376</v>
+        <v>519408</v>
       </c>
       <c r="R32" t="n">
-        <v>7034350</v>
+        <v>7034486</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3955,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,10 +3982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467574</v>
+        <v>120467627</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3998,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519385</v>
+        <v>519361</v>
       </c>
       <c r="R33" t="n">
-        <v>7034219</v>
+        <v>7034385</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4048,11 +4058,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467575</v>
+        <v>120467598</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519384</v>
+        <v>519500</v>
       </c>
       <c r="R34" t="n">
-        <v>7034223</v>
+        <v>7034377</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4186,7 +4191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467565</v>
+        <v>120467571</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519363</v>
+        <v>519383</v>
       </c>
       <c r="R35" t="n">
-        <v>7034334</v>
+        <v>7034199</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4271,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,7 +4298,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467587</v>
+        <v>120467568</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4333,7 +4338,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519412</v>
+        <v>519370</v>
       </c>
       <c r="R36" t="n">
         <v>7034235</v>
@@ -4400,7 +4405,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467554</v>
+        <v>120467592</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4440,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519486</v>
+        <v>519472</v>
       </c>
       <c r="R37" t="n">
-        <v>7034475</v>
+        <v>7034318</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4485,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4507,7 +4512,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467571</v>
+        <v>120467580</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4547,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519383</v>
+        <v>519388</v>
       </c>
       <c r="R38" t="n">
-        <v>7034199</v>
+        <v>7034221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4592,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4614,7 +4619,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467581</v>
+        <v>120467593</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4654,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519389</v>
+        <v>519467</v>
       </c>
       <c r="R39" t="n">
-        <v>7034222</v>
+        <v>7034318</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4699,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4721,7 +4726,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467566</v>
+        <v>120467577</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4761,10 +4766,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519393</v>
+        <v>519386</v>
       </c>
       <c r="R40" t="n">
-        <v>7034297</v>
+        <v>7034229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,7 +4806,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4828,7 +4833,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467562</v>
+        <v>120467567</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519399</v>
+        <v>519393</v>
       </c>
       <c r="R41" t="n">
-        <v>7034481</v>
+        <v>7034245</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4935,10 +4940,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467593</v>
+        <v>120467626</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4951,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4975,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519467</v>
+        <v>519435</v>
       </c>
       <c r="R42" t="n">
-        <v>7034318</v>
+        <v>7034340</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5011,11 +5016,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467584</v>
+        <v>120467572</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519403</v>
+        <v>519384</v>
       </c>
       <c r="R43" t="n">
-        <v>7034216</v>
+        <v>7034205</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5149,7 +5149,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467578</v>
+        <v>120467559</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519389</v>
+        <v>519429</v>
       </c>
       <c r="R44" t="n">
-        <v>7034229</v>
+        <v>7034461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5256,7 +5256,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467576</v>
+        <v>120467597</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519383</v>
+        <v>519497</v>
       </c>
       <c r="R45" t="n">
-        <v>7034225</v>
+        <v>7034345</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5363,7 +5363,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467558</v>
+        <v>120467555</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519402</v>
+        <v>519477</v>
       </c>
       <c r="R46" t="n">
-        <v>7034350</v>
+        <v>7034429</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5470,7 +5470,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467569</v>
+        <v>120467589</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519355</v>
+        <v>519426</v>
       </c>
       <c r="R47" t="n">
-        <v>7034201</v>
+        <v>7034284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467557</v>
+        <v>120467579</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519397</v>
+        <v>519392</v>
       </c>
       <c r="R48" t="n">
-        <v>7034351</v>
+        <v>7034219</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467567</v>
+        <v>120467583</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519393</v>
+        <v>519401</v>
       </c>
       <c r="R49" t="n">
-        <v>7034245</v>
+        <v>7034214</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467590</v>
+        <v>120467628</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519424</v>
+        <v>519399</v>
       </c>
       <c r="R15" t="n">
-        <v>7034288</v>
+        <v>7034196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467562</v>
+        <v>120467590</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519399</v>
+        <v>519424</v>
       </c>
       <c r="R16" t="n">
-        <v>7034481</v>
+        <v>7034288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467557</v>
+        <v>120467562</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519397</v>
+        <v>519399</v>
       </c>
       <c r="R17" t="n">
-        <v>7034351</v>
+        <v>7034481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467554</v>
+        <v>120467557</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519486</v>
+        <v>519397</v>
       </c>
       <c r="R18" t="n">
-        <v>7034475</v>
+        <v>7034351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467628</v>
+        <v>120467554</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519399</v>
+        <v>519486</v>
       </c>
       <c r="R19" t="n">
-        <v>7034196</v>
+        <v>7034475</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2560,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467574</v>
+        <v>120467570</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519385</v>
+        <v>519395</v>
       </c>
       <c r="R2" t="n">
-        <v>7034219</v>
+        <v>7034197</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467575</v>
+        <v>120467571</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519384</v>
+        <v>519383</v>
       </c>
       <c r="R3" t="n">
-        <v>7034223</v>
+        <v>7034199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467553</v>
+        <v>120467556</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519489</v>
+        <v>519458</v>
       </c>
       <c r="R4" t="n">
-        <v>7034525</v>
+        <v>7034427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467584</v>
+        <v>120467559</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519403</v>
+        <v>519429</v>
       </c>
       <c r="R5" t="n">
-        <v>7034216</v>
+        <v>7034461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467629</v>
+        <v>120467568</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519509</v>
+        <v>519370</v>
       </c>
       <c r="R6" t="n">
-        <v>7034395</v>
+        <v>7034235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467582</v>
+        <v>120467576</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,7 +1250,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519393</v>
+        <v>519383</v>
       </c>
       <c r="R7" t="n">
         <v>7034225</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467569</v>
+        <v>120467580</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519355</v>
+        <v>519388</v>
       </c>
       <c r="R8" t="n">
-        <v>7034201</v>
+        <v>7034221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467573</v>
+        <v>120467596</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519380</v>
+        <v>519510</v>
       </c>
       <c r="R9" t="n">
-        <v>7034214</v>
+        <v>7034345</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467560</v>
+        <v>120467578</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519436</v>
+        <v>519389</v>
       </c>
       <c r="R10" t="n">
-        <v>7034470</v>
+        <v>7034229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467566</v>
+        <v>120467587</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519393</v>
+        <v>519412</v>
       </c>
       <c r="R11" t="n">
-        <v>7034297</v>
+        <v>7034235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467576</v>
+        <v>120467572</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519383</v>
+        <v>519384</v>
       </c>
       <c r="R12" t="n">
-        <v>7034225</v>
+        <v>7034205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467558</v>
+        <v>120467593</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519402</v>
+        <v>519467</v>
       </c>
       <c r="R13" t="n">
-        <v>7034350</v>
+        <v>7034318</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467556</v>
+        <v>120467573</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519458</v>
+        <v>519380</v>
       </c>
       <c r="R14" t="n">
-        <v>7034427</v>
+        <v>7034214</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467628</v>
+        <v>120467627</v>
       </c>
       <c r="B15" t="n">
         <v>90598</v>
@@ -2101,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519399</v>
+        <v>519361</v>
       </c>
       <c r="R15" t="n">
-        <v>7034196</v>
+        <v>7034385</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467590</v>
+        <v>120467582</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519424</v>
+        <v>519393</v>
       </c>
       <c r="R16" t="n">
-        <v>7034288</v>
+        <v>7034225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467562</v>
+        <v>120467553</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519399</v>
+        <v>519489</v>
       </c>
       <c r="R17" t="n">
-        <v>7034481</v>
+        <v>7034525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467557</v>
+        <v>120467591</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519397</v>
+        <v>519446</v>
       </c>
       <c r="R18" t="n">
-        <v>7034351</v>
+        <v>7034304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467554</v>
+        <v>120467597</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519486</v>
+        <v>519497</v>
       </c>
       <c r="R19" t="n">
-        <v>7034475</v>
+        <v>7034345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467595</v>
+        <v>120467628</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519487</v>
+        <v>519399</v>
       </c>
       <c r="R20" t="n">
-        <v>7034345</v>
+        <v>7034196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,11 +2672,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467570</v>
+        <v>120467569</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519395</v>
+        <v>519355</v>
       </c>
       <c r="R21" t="n">
-        <v>7034197</v>
+        <v>7034201</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467565</v>
+        <v>120467566</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519363</v>
+        <v>519393</v>
       </c>
       <c r="R22" t="n">
-        <v>7034334</v>
+        <v>7034297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467594</v>
+        <v>120467598</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519475</v>
+        <v>519500</v>
       </c>
       <c r="R23" t="n">
-        <v>7034336</v>
+        <v>7034377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467564</v>
+        <v>120467581</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519376</v>
+        <v>519389</v>
       </c>
       <c r="R24" t="n">
-        <v>7034350</v>
+        <v>7034222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467578</v>
+        <v>120467589</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519389</v>
+        <v>519426</v>
       </c>
       <c r="R25" t="n">
-        <v>7034229</v>
+        <v>7034284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467587</v>
+        <v>120467579</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519412</v>
+        <v>519392</v>
       </c>
       <c r="R26" t="n">
-        <v>7034235</v>
+        <v>7034219</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467588</v>
+        <v>120467554</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519413</v>
+        <v>519486</v>
       </c>
       <c r="R27" t="n">
-        <v>7034235</v>
+        <v>7034475</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,7 +3447,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467591</v>
+        <v>120467592</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519446</v>
+        <v>519472</v>
       </c>
       <c r="R28" t="n">
-        <v>7034304</v>
+        <v>7034318</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,7 +3554,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467596</v>
+        <v>120467567</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519510</v>
+        <v>519393</v>
       </c>
       <c r="R29" t="n">
-        <v>7034345</v>
+        <v>7034245</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467581</v>
+        <v>120467629</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519389</v>
+        <v>519509</v>
       </c>
       <c r="R30" t="n">
-        <v>7034222</v>
+        <v>7034395</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,11 +3737,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467586</v>
+        <v>120467575</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519422</v>
+        <v>519384</v>
       </c>
       <c r="R31" t="n">
-        <v>7034236</v>
+        <v>7034223</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467561</v>
+        <v>120467565</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519408</v>
+        <v>519363</v>
       </c>
       <c r="R32" t="n">
-        <v>7034486</v>
+        <v>7034334</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,10 +3977,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467627</v>
+        <v>120467588</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,21 +3993,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519361</v>
+        <v>519413</v>
       </c>
       <c r="R33" t="n">
-        <v>7034385</v>
+        <v>7034235</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,6 +4053,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467598</v>
+        <v>120467562</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519500</v>
+        <v>519399</v>
       </c>
       <c r="R34" t="n">
-        <v>7034377</v>
+        <v>7034481</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467571</v>
+        <v>120467594</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519383</v>
+        <v>519475</v>
       </c>
       <c r="R35" t="n">
-        <v>7034199</v>
+        <v>7034336</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467568</v>
+        <v>120467558</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519370</v>
+        <v>519402</v>
       </c>
       <c r="R36" t="n">
-        <v>7034235</v>
+        <v>7034350</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467592</v>
+        <v>120467574</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519472</v>
+        <v>519385</v>
       </c>
       <c r="R37" t="n">
-        <v>7034318</v>
+        <v>7034219</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,7 +4512,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467580</v>
+        <v>120467557</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519388</v>
+        <v>519397</v>
       </c>
       <c r="R38" t="n">
-        <v>7034221</v>
+        <v>7034351</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,7 +4619,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467593</v>
+        <v>120467555</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519467</v>
+        <v>519477</v>
       </c>
       <c r="R39" t="n">
-        <v>7034318</v>
+        <v>7034429</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467577</v>
+        <v>120467561</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519386</v>
+        <v>519408</v>
       </c>
       <c r="R40" t="n">
-        <v>7034229</v>
+        <v>7034486</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4833,7 +4833,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467567</v>
+        <v>120467560</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519393</v>
+        <v>519436</v>
       </c>
       <c r="R41" t="n">
-        <v>7034245</v>
+        <v>7034470</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4940,10 +4940,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467626</v>
+        <v>120467564</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519435</v>
+        <v>519376</v>
       </c>
       <c r="R42" t="n">
-        <v>7034340</v>
+        <v>7034350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5016,6 +5016,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5047,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467572</v>
+        <v>120467595</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5082,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519384</v>
+        <v>519487</v>
       </c>
       <c r="R43" t="n">
-        <v>7034205</v>
+        <v>7034345</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5127,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5149,7 +5154,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467559</v>
+        <v>120467590</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5189,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519429</v>
+        <v>519424</v>
       </c>
       <c r="R44" t="n">
-        <v>7034461</v>
+        <v>7034288</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5256,7 +5261,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467597</v>
+        <v>120467583</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519497</v>
+        <v>519401</v>
       </c>
       <c r="R45" t="n">
-        <v>7034345</v>
+        <v>7034214</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5341,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5363,7 +5368,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467555</v>
+        <v>120467584</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5403,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519477</v>
+        <v>519403</v>
       </c>
       <c r="R46" t="n">
-        <v>7034429</v>
+        <v>7034216</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5448,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5470,10 +5475,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467589</v>
+        <v>120467626</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5486,21 +5491,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5510,10 +5515,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519426</v>
+        <v>519435</v>
       </c>
       <c r="R47" t="n">
-        <v>7034284</v>
+        <v>7034340</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5546,11 +5551,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5577,7 +5577,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467579</v>
+        <v>120467586</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519392</v>
+        <v>519422</v>
       </c>
       <c r="R48" t="n">
-        <v>7034219</v>
+        <v>7034236</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467583</v>
+        <v>120467577</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519401</v>
+        <v>519386</v>
       </c>
       <c r="R49" t="n">
-        <v>7034214</v>
+        <v>7034229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467570</v>
+        <v>120467628</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519395</v>
+        <v>519399</v>
       </c>
       <c r="R2" t="n">
-        <v>7034197</v>
+        <v>7034196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467571</v>
+        <v>120467626</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519383</v>
+        <v>519435</v>
       </c>
       <c r="R3" t="n">
-        <v>7034199</v>
+        <v>7034340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467556</v>
+        <v>120467566</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519458</v>
+        <v>519393</v>
       </c>
       <c r="R4" t="n">
-        <v>7034427</v>
+        <v>7034297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467559</v>
+        <v>120467553</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519429</v>
+        <v>519489</v>
       </c>
       <c r="R5" t="n">
-        <v>7034461</v>
+        <v>7034525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467568</v>
+        <v>120467572</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519370</v>
+        <v>519384</v>
       </c>
       <c r="R6" t="n">
-        <v>7034235</v>
+        <v>7034205</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467576</v>
+        <v>120467583</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519383</v>
+        <v>519401</v>
       </c>
       <c r="R7" t="n">
-        <v>7034225</v>
+        <v>7034214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467580</v>
+        <v>120467592</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519388</v>
+        <v>519472</v>
       </c>
       <c r="R8" t="n">
-        <v>7034221</v>
+        <v>7034318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467596</v>
+        <v>120467576</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519510</v>
+        <v>519383</v>
       </c>
       <c r="R9" t="n">
-        <v>7034345</v>
+        <v>7034225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467578</v>
+        <v>120467597</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1571,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519389</v>
+        <v>519497</v>
       </c>
       <c r="R10" t="n">
-        <v>7034229</v>
+        <v>7034345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467587</v>
+        <v>120467559</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1678,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519412</v>
+        <v>519429</v>
       </c>
       <c r="R11" t="n">
-        <v>7034235</v>
+        <v>7034461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467572</v>
+        <v>120467593</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519384</v>
+        <v>519467</v>
       </c>
       <c r="R12" t="n">
-        <v>7034205</v>
+        <v>7034318</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467593</v>
+        <v>120467578</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1892,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519467</v>
+        <v>519389</v>
       </c>
       <c r="R13" t="n">
-        <v>7034318</v>
+        <v>7034229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467573</v>
+        <v>120467581</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1999,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519380</v>
+        <v>519389</v>
       </c>
       <c r="R14" t="n">
-        <v>7034214</v>
+        <v>7034222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467627</v>
+        <v>120467589</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519361</v>
+        <v>519426</v>
       </c>
       <c r="R15" t="n">
-        <v>7034385</v>
+        <v>7034284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467582</v>
+        <v>120467584</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519393</v>
+        <v>519403</v>
       </c>
       <c r="R16" t="n">
-        <v>7034225</v>
+        <v>7034216</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467553</v>
+        <v>120467555</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519489</v>
+        <v>519477</v>
       </c>
       <c r="R17" t="n">
-        <v>7034525</v>
+        <v>7034429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467591</v>
+        <v>120467567</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519446</v>
+        <v>519393</v>
       </c>
       <c r="R18" t="n">
-        <v>7034304</v>
+        <v>7034245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467597</v>
+        <v>120467561</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519497</v>
+        <v>519408</v>
       </c>
       <c r="R19" t="n">
-        <v>7034345</v>
+        <v>7034486</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467628</v>
+        <v>120467562</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2639,7 +2634,7 @@
         <v>519399</v>
       </c>
       <c r="R20" t="n">
-        <v>7034196</v>
+        <v>7034481</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467569</v>
+        <v>120467574</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519355</v>
+        <v>519385</v>
       </c>
       <c r="R21" t="n">
-        <v>7034201</v>
+        <v>7034219</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467566</v>
+        <v>120467570</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519393</v>
+        <v>519395</v>
       </c>
       <c r="R22" t="n">
-        <v>7034297</v>
+        <v>7034197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467598</v>
+        <v>120467560</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519500</v>
+        <v>519436</v>
       </c>
       <c r="R23" t="n">
-        <v>7034377</v>
+        <v>7034470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467581</v>
+        <v>120467582</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519389</v>
+        <v>519393</v>
       </c>
       <c r="R24" t="n">
-        <v>7034222</v>
+        <v>7034225</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467589</v>
+        <v>120467590</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519426</v>
+        <v>519424</v>
       </c>
       <c r="R25" t="n">
-        <v>7034284</v>
+        <v>7034288</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467579</v>
+        <v>120467591</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519392</v>
+        <v>519446</v>
       </c>
       <c r="R26" t="n">
-        <v>7034219</v>
+        <v>7034304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467554</v>
+        <v>120467569</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519486</v>
+        <v>519355</v>
       </c>
       <c r="R27" t="n">
-        <v>7034475</v>
+        <v>7034201</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467592</v>
+        <v>120467577</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519472</v>
+        <v>519386</v>
       </c>
       <c r="R28" t="n">
-        <v>7034318</v>
+        <v>7034229</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,7 +3554,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467567</v>
+        <v>120467564</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519393</v>
+        <v>519376</v>
       </c>
       <c r="R29" t="n">
-        <v>7034245</v>
+        <v>7034350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467629</v>
+        <v>120467598</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519509</v>
+        <v>519500</v>
       </c>
       <c r="R30" t="n">
-        <v>7034395</v>
+        <v>7034377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,6 +3737,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467575</v>
+        <v>120467556</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3803,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519384</v>
+        <v>519458</v>
       </c>
       <c r="R31" t="n">
-        <v>7034223</v>
+        <v>7034427</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3848,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467565</v>
+        <v>120467627</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519363</v>
+        <v>519361</v>
       </c>
       <c r="R32" t="n">
-        <v>7034334</v>
+        <v>7034385</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,11 +3951,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3977,7 +3977,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467588</v>
+        <v>120467594</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519413</v>
+        <v>519475</v>
       </c>
       <c r="R33" t="n">
-        <v>7034235</v>
+        <v>7034336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467562</v>
+        <v>120467573</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519399</v>
+        <v>519380</v>
       </c>
       <c r="R34" t="n">
-        <v>7034481</v>
+        <v>7034214</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,7 +4191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467594</v>
+        <v>120467565</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519475</v>
+        <v>519363</v>
       </c>
       <c r="R35" t="n">
-        <v>7034336</v>
+        <v>7034334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4298,7 +4298,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467558</v>
+        <v>120467568</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519402</v>
+        <v>519370</v>
       </c>
       <c r="R36" t="n">
-        <v>7034350</v>
+        <v>7034235</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467574</v>
+        <v>120467595</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519385</v>
+        <v>519487</v>
       </c>
       <c r="R37" t="n">
-        <v>7034219</v>
+        <v>7034345</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,7 +4512,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467557</v>
+        <v>120467587</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519397</v>
+        <v>519412</v>
       </c>
       <c r="R38" t="n">
-        <v>7034351</v>
+        <v>7034235</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467555</v>
+        <v>120467579</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519477</v>
+        <v>519392</v>
       </c>
       <c r="R39" t="n">
-        <v>7034429</v>
+        <v>7034219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4726,10 +4726,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467561</v>
+        <v>120467629</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4742,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519408</v>
+        <v>519509</v>
       </c>
       <c r="R40" t="n">
-        <v>7034486</v>
+        <v>7034395</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,11 +4802,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4833,7 +4828,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467560</v>
+        <v>120467558</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519436</v>
+        <v>519402</v>
       </c>
       <c r="R41" t="n">
-        <v>7034470</v>
+        <v>7034350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4940,7 +4935,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467564</v>
+        <v>120467596</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4980,10 +4975,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519376</v>
+        <v>519510</v>
       </c>
       <c r="R42" t="n">
-        <v>7034350</v>
+        <v>7034345</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5047,7 +5042,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467595</v>
+        <v>120467557</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5087,10 +5082,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519487</v>
+        <v>519397</v>
       </c>
       <c r="R43" t="n">
-        <v>7034345</v>
+        <v>7034351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,7 +5122,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5154,7 +5149,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467590</v>
+        <v>120467580</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5194,10 +5189,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519424</v>
+        <v>519388</v>
       </c>
       <c r="R44" t="n">
-        <v>7034288</v>
+        <v>7034221</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5234,7 +5229,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,7 +5256,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467583</v>
+        <v>120467575</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519401</v>
+        <v>519384</v>
       </c>
       <c r="R45" t="n">
-        <v>7034214</v>
+        <v>7034223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5336,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,7 +5363,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467584</v>
+        <v>120467586</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5408,10 +5403,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519403</v>
+        <v>519422</v>
       </c>
       <c r="R46" t="n">
-        <v>7034216</v>
+        <v>7034236</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,10 +5470,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467626</v>
+        <v>120467571</v>
       </c>
       <c r="B47" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5491,21 +5486,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5515,10 +5510,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519435</v>
+        <v>519383</v>
       </c>
       <c r="R47" t="n">
-        <v>7034340</v>
+        <v>7034199</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5551,6 +5546,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5577,7 +5577,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467586</v>
+        <v>120467588</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519422</v>
+        <v>519413</v>
       </c>
       <c r="R48" t="n">
-        <v>7034236</v>
+        <v>7034235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5684,7 +5684,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467577</v>
+        <v>120467554</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519386</v>
+        <v>519486</v>
       </c>
       <c r="R49" t="n">
-        <v>7034229</v>
+        <v>7034475</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467598</v>
+        <v>120467627</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519500</v>
+        <v>519361</v>
       </c>
       <c r="R30" t="n">
-        <v>7034377</v>
+        <v>7034385</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,11 +3737,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467556</v>
+        <v>120467598</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519458</v>
+        <v>519500</v>
       </c>
       <c r="R31" t="n">
-        <v>7034427</v>
+        <v>7034377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3843,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467627</v>
+        <v>120467556</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519361</v>
+        <v>519458</v>
       </c>
       <c r="R32" t="n">
-        <v>7034385</v>
+        <v>7034427</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3951,6 +3946,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5789,6 +5789,816 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128047055</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>519360</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7034389</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128047087</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>504</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>519521</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7034534</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128047062</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>519477</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7034364</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128047030</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>519513</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7034346</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128047088</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98479</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>519521</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7034534</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128047077</v>
+      </c>
+      <c r="B55" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>519501</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7034494</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128047034</v>
+      </c>
+      <c r="B56" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>519461</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7034370</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128047044</v>
+      </c>
+      <c r="B57" t="n">
+        <v>75144</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>519462</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7034369</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98362</v>
+        <v>98365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>128047062</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,38 +6196,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B54" t="n">
-        <v>98479</v>
+        <v>82864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6235,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R54" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6298,37 +6297,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>82861</v>
+        <v>98482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R55" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6402,7 +6402,7 @@
         <v>128047034</v>
       </c>
       <c r="B56" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>128047044</v>
       </c>
       <c r="B57" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>128047062</v>
       </c>
       <c r="B52" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>128047077</v>
       </c>
       <c r="B54" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>128047034</v>
       </c>
       <c r="B56" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>128047044</v>
       </c>
       <c r="B57" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>98374</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -6196,37 +6196,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B54" t="n">
-        <v>82870</v>
+        <v>98491</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6234,10 +6235,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R54" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6297,38 +6298,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B55" t="n">
-        <v>98491</v>
+        <v>82870</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R55" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98374</v>
+        <v>98375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,38 +6196,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B54" t="n">
-        <v>98491</v>
+        <v>82870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6235,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R54" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6298,37 +6297,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>82870</v>
+        <v>98492</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R55" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98375</v>
+        <v>98376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -6196,37 +6196,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B54" t="n">
-        <v>82870</v>
+        <v>98493</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6234,10 +6235,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R54" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6297,38 +6298,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B55" t="n">
-        <v>98493</v>
+        <v>82870</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R55" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -6196,38 +6196,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B54" t="n">
-        <v>98493</v>
+        <v>82870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6235,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R54" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6298,37 +6297,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>82870</v>
+        <v>98493</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R55" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>128047062</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>128047088</v>
       </c>
       <c r="B54" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>128047077</v>
       </c>
       <c r="B55" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>128047034</v>
       </c>
       <c r="B56" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>128047044</v>
       </c>
       <c r="B57" t="n">
-        <v>75153</v>
+        <v>75156</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98384</v>
+        <v>98477</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>128047062</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,38 +6196,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B54" t="n">
-        <v>98501</v>
+        <v>82942</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6235,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R54" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6298,37 +6297,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B55" t="n">
-        <v>82873</v>
+        <v>98594</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R55" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6402,7 +6402,7 @@
         <v>128047034</v>
       </c>
       <c r="B56" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>128047044</v>
       </c>
       <c r="B57" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -6196,37 +6196,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128047077</v>
+        <v>128047088</v>
       </c>
       <c r="B54" t="n">
-        <v>82942</v>
+        <v>98594</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6234,10 +6235,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519501</v>
+        <v>519521</v>
       </c>
       <c r="R54" t="n">
-        <v>7034494</v>
+        <v>7034534</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6297,38 +6298,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128047088</v>
+        <v>128047077</v>
       </c>
       <c r="B55" t="n">
-        <v>98594</v>
+        <v>82942</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519521</v>
+        <v>519501</v>
       </c>
       <c r="R55" t="n">
-        <v>7034534</v>
+        <v>7034494</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -5794,7 +5794,7 @@
         <v>128047055</v>
       </c>
       <c r="B50" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>128047087</v>
       </c>
       <c r="B51" t="n">
-        <v>98477</v>
+        <v>98491</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>128047062</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>128047030</v>
       </c>
       <c r="B53" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>128047088</v>
       </c>
       <c r="B54" t="n">
-        <v>98594</v>
+        <v>98608</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>128047077</v>
       </c>
       <c r="B55" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>128047034</v>
       </c>
       <c r="B56" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>128047044</v>
       </c>
       <c r="B57" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467629</v>
+        <v>128047087</v>
       </c>
       <c r="B2" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519509</v>
+        <v>519521</v>
       </c>
       <c r="R2" t="n">
-        <v>7034395</v>
+        <v>7034534</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,71 +758,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467560</v>
+        <v>128047095</v>
       </c>
       <c r="B3" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519436</v>
+        <v>519507</v>
       </c>
       <c r="R3" t="n">
-        <v>7034470</v>
+        <v>7034546</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,33 +860,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467581</v>
+        <v>128047030</v>
       </c>
       <c r="B4" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +890,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519389</v>
+        <v>519513</v>
       </c>
       <c r="R4" t="n">
-        <v>7034222</v>
+        <v>7034346</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,17 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,33 +961,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467556</v>
+        <v>128047034</v>
       </c>
       <c r="B5" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +991,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519458</v>
+        <v>519461</v>
       </c>
       <c r="R5" t="n">
-        <v>7034427</v>
+        <v>7034370</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,17 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,33 +1062,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467553</v>
+        <v>128047077</v>
       </c>
       <c r="B6" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1092,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519489</v>
+        <v>519501</v>
       </c>
       <c r="R6" t="n">
-        <v>7034525</v>
+        <v>7034494</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,17 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,71 +1163,70 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467579</v>
+        <v>128047062</v>
       </c>
       <c r="B7" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519392</v>
+        <v>519477</v>
       </c>
       <c r="R7" t="n">
-        <v>7034219</v>
+        <v>7034364</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,17 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,33 +1264,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467575</v>
+        <v>128047044</v>
       </c>
       <c r="B8" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,37 +1294,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519384</v>
+        <v>519462</v>
       </c>
       <c r="R8" t="n">
-        <v>7034223</v>
+        <v>7034369</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,17 +1351,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,33 +1365,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467598</v>
+        <v>120467553</v>
       </c>
       <c r="B9" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519500</v>
+        <v>519489</v>
       </c>
       <c r="R9" t="n">
-        <v>7034377</v>
+        <v>7034525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467582</v>
+        <v>120467554</v>
       </c>
       <c r="B10" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519393</v>
+        <v>519486</v>
       </c>
       <c r="R10" t="n">
-        <v>7034225</v>
+        <v>7034475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467566</v>
+        <v>120467555</v>
       </c>
       <c r="B11" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519393</v>
+        <v>519477</v>
       </c>
       <c r="R11" t="n">
-        <v>7034297</v>
+        <v>7034429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1663,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467583</v>
+        <v>120467556</v>
       </c>
       <c r="B12" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519401</v>
+        <v>519458</v>
       </c>
       <c r="R12" t="n">
-        <v>7034214</v>
+        <v>7034427</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467558</v>
+        <v>120467557</v>
       </c>
       <c r="B13" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519402</v>
+        <v>519397</v>
       </c>
       <c r="R13" t="n">
-        <v>7034350</v>
+        <v>7034351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,15 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467576</v>
+        <v>120467558</v>
       </c>
       <c r="B14" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519383</v>
+        <v>519402</v>
       </c>
       <c r="R14" t="n">
-        <v>7034225</v>
+        <v>7034350</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,15 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467571</v>
+        <v>120467559</v>
       </c>
       <c r="B15" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519383</v>
+        <v>519429</v>
       </c>
       <c r="R15" t="n">
-        <v>7034199</v>
+        <v>7034461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,15 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467587</v>
+        <v>120467560</v>
       </c>
       <c r="B16" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519412</v>
+        <v>519436</v>
       </c>
       <c r="R16" t="n">
-        <v>7034235</v>
+        <v>7034470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,15 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467626</v>
+        <v>120467561</v>
       </c>
       <c r="B17" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519435</v>
+        <v>519408</v>
       </c>
       <c r="R17" t="n">
-        <v>7034340</v>
+        <v>7034486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2271,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,15 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467574</v>
+        <v>120467562</v>
       </c>
       <c r="B18" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519385</v>
+        <v>519399</v>
       </c>
       <c r="R18" t="n">
-        <v>7034219</v>
+        <v>7034481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,15 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467596</v>
+        <v>120467564</v>
       </c>
       <c r="B19" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519510</v>
+        <v>519376</v>
       </c>
       <c r="R19" t="n">
-        <v>7034345</v>
+        <v>7034350</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,15 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467578</v>
+        <v>120467565</v>
       </c>
       <c r="B20" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519389</v>
+        <v>519363</v>
       </c>
       <c r="R20" t="n">
-        <v>7034229</v>
+        <v>7034334</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,15 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467561</v>
+        <v>120467566</v>
       </c>
       <c r="B21" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519408</v>
+        <v>519393</v>
       </c>
       <c r="R21" t="n">
-        <v>7034486</v>
+        <v>7034297</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,15 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467554</v>
+        <v>120467567</v>
       </c>
       <c r="B22" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519486</v>
+        <v>519393</v>
       </c>
       <c r="R22" t="n">
-        <v>7034475</v>
+        <v>7034245</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,15 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467592</v>
+        <v>120467568</v>
       </c>
       <c r="B23" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,10 +2847,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519472</v>
+        <v>519370</v>
       </c>
       <c r="R23" t="n">
-        <v>7034318</v>
+        <v>7034235</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2887,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,15 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467594</v>
+        <v>120467569</v>
       </c>
       <c r="B24" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519475</v>
+        <v>519355</v>
       </c>
       <c r="R24" t="n">
-        <v>7034336</v>
+        <v>7034201</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,12 +3019,7 @@
         <v>120467570</v>
       </c>
       <c r="B25" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,15 +3118,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467569</v>
+        <v>120467571</v>
       </c>
       <c r="B26" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519355</v>
+        <v>519383</v>
       </c>
       <c r="R26" t="n">
-        <v>7034201</v>
+        <v>7034199</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,15 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467628</v>
+        <v>120467572</v>
       </c>
       <c r="B27" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3231,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519399</v>
+        <v>519384</v>
       </c>
       <c r="R27" t="n">
-        <v>7034196</v>
+        <v>7034205</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,6 +3291,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,15 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467590</v>
+        <v>120467573</v>
       </c>
       <c r="B28" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519424</v>
+        <v>519380</v>
       </c>
       <c r="R28" t="n">
-        <v>7034288</v>
+        <v>7034214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3397,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,15 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467559</v>
+        <v>120467574</v>
       </c>
       <c r="B29" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519429</v>
+        <v>519385</v>
       </c>
       <c r="R29" t="n">
-        <v>7034461</v>
+        <v>7034219</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,15 +3526,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467573</v>
+        <v>120467575</v>
       </c>
       <c r="B30" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,10 +3561,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519380</v>
+        <v>519384</v>
       </c>
       <c r="R30" t="n">
-        <v>7034214</v>
+        <v>7034223</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3601,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,15 +3628,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467584</v>
+        <v>120467576</v>
       </c>
       <c r="B31" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519403</v>
+        <v>519383</v>
       </c>
       <c r="R31" t="n">
-        <v>7034216</v>
+        <v>7034225</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3703,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,15 +3730,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467595</v>
+        <v>120467577</v>
       </c>
       <c r="B32" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519487</v>
+        <v>519386</v>
       </c>
       <c r="R32" t="n">
-        <v>7034345</v>
+        <v>7034229</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3977,15 +3832,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467597</v>
+        <v>120467578</v>
       </c>
       <c r="B33" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,10 +3867,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519497</v>
+        <v>519389</v>
       </c>
       <c r="R33" t="n">
-        <v>7034345</v>
+        <v>7034229</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +3907,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,15 +3934,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467572</v>
+        <v>120467579</v>
       </c>
       <c r="B34" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519384</v>
+        <v>519392</v>
       </c>
       <c r="R34" t="n">
-        <v>7034205</v>
+        <v>7034219</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,15 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467577</v>
+        <v>120467580</v>
       </c>
       <c r="B35" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519386</v>
+        <v>519388</v>
       </c>
       <c r="R35" t="n">
-        <v>7034229</v>
+        <v>7034221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4298,15 +4138,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467555</v>
+        <v>120467581</v>
       </c>
       <c r="B36" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4338,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519477</v>
+        <v>519389</v>
       </c>
       <c r="R36" t="n">
-        <v>7034429</v>
+        <v>7034222</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,7 +4213,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,15 +4240,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467565</v>
+        <v>120467582</v>
       </c>
       <c r="B37" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519363</v>
+        <v>519393</v>
       </c>
       <c r="R37" t="n">
-        <v>7034334</v>
+        <v>7034225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,7 +4315,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,15 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467589</v>
+        <v>120467583</v>
       </c>
       <c r="B38" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,10 +4377,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519426</v>
+        <v>519401</v>
       </c>
       <c r="R38" t="n">
-        <v>7034284</v>
+        <v>7034214</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4417,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,15 +4444,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467562</v>
+        <v>120467584</v>
       </c>
       <c r="B39" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,10 +4479,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519399</v>
+        <v>519403</v>
       </c>
       <c r="R39" t="n">
-        <v>7034481</v>
+        <v>7034216</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,7 +4519,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4726,15 +4546,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467567</v>
+        <v>120467586</v>
       </c>
       <c r="B40" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519393</v>
+        <v>519422</v>
       </c>
       <c r="R40" t="n">
-        <v>7034245</v>
+        <v>7034236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4833,15 +4648,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467568</v>
+        <v>120467587</v>
       </c>
       <c r="B41" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4873,7 +4683,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519370</v>
+        <v>519412</v>
       </c>
       <c r="R41" t="n">
         <v>7034235</v>
@@ -4940,15 +4750,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467593</v>
+        <v>120467588</v>
       </c>
       <c r="B42" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4980,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519467</v>
+        <v>519413</v>
       </c>
       <c r="R42" t="n">
-        <v>7034318</v>
+        <v>7034235</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,7 +4825,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5047,15 +4852,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467588</v>
+        <v>120467589</v>
       </c>
       <c r="B43" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5087,10 +4887,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519413</v>
+        <v>519426</v>
       </c>
       <c r="R43" t="n">
-        <v>7034235</v>
+        <v>7034284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,7 +4927,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5154,15 +4954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467580</v>
+        <v>120467590</v>
       </c>
       <c r="B44" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5194,10 +4989,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519388</v>
+        <v>519424</v>
       </c>
       <c r="R44" t="n">
-        <v>7034221</v>
+        <v>7034288</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5234,7 +5029,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,15 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467564</v>
+        <v>120467591</v>
       </c>
       <c r="B45" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519376</v>
+        <v>519446</v>
       </c>
       <c r="R45" t="n">
-        <v>7034350</v>
+        <v>7034304</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5131,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,15 +5158,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467591</v>
+        <v>120467592</v>
       </c>
       <c r="B46" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,10 +5193,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519446</v>
+        <v>519472</v>
       </c>
       <c r="R46" t="n">
-        <v>7034304</v>
+        <v>7034318</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5233,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,15 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467586</v>
+        <v>120467593</v>
       </c>
       <c r="B47" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519422</v>
+        <v>519467</v>
       </c>
       <c r="R47" t="n">
-        <v>7034236</v>
+        <v>7034318</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5335,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5582,15 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467627</v>
+        <v>120467594</v>
       </c>
       <c r="B48" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5622,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519361</v>
+        <v>519475</v>
       </c>
       <c r="R48" t="n">
-        <v>7034385</v>
+        <v>7034336</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5658,6 +5433,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5684,15 +5464,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467557</v>
+        <v>120467595</v>
       </c>
       <c r="B49" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5724,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519397</v>
+        <v>519487</v>
       </c>
       <c r="R49" t="n">
-        <v>7034351</v>
+        <v>7034345</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,7 +5539,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5791,10 +5566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128047055</v>
+        <v>120467596</v>
       </c>
       <c r="B50" t="n">
-        <v>91482</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5802,40 +5577,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Finnboriset, Jmt</t>
+          <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519360</v>
+        <v>519510</v>
       </c>
       <c r="R50" t="n">
-        <v>7034389</v>
+        <v>7034345</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5859,12 +5631,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,71 +5650,66 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128047087</v>
+        <v>120467597</v>
       </c>
       <c r="B51" t="n">
-        <v>98491</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Finnboriset, Jmt</t>
+          <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519521</v>
+        <v>519497</v>
       </c>
       <c r="R51" t="n">
-        <v>7034534</v>
+        <v>7034345</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5961,12 +5733,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,29 +5752,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128047062</v>
+        <v>120467598</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6005,40 +5781,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Finnboriset, Jmt</t>
+          <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519477</v>
+        <v>519500</v>
       </c>
       <c r="R52" t="n">
-        <v>7034364</v>
+        <v>7034377</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6062,12 +5835,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6076,56 +5854,56 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128047030</v>
+        <v>128047088</v>
       </c>
       <c r="B53" t="n">
-        <v>91464</v>
+        <v>99142</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6133,10 +5911,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519513</v>
+        <v>519521</v>
       </c>
       <c r="R53" t="n">
-        <v>7034346</v>
+        <v>7034534</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6193,411 +5971,6 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>128047088</v>
-      </c>
-      <c r="B54" t="n">
-        <v>98608</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Finnboriset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>519521</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7034534</v>
-      </c>
-      <c r="S54" t="n">
-        <v>25</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>128047077</v>
-      </c>
-      <c r="B55" t="n">
-        <v>82946</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Finnboriset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>519501</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7034494</v>
-      </c>
-      <c r="S55" t="n">
-        <v>25</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>128047034</v>
-      </c>
-      <c r="B56" t="n">
-        <v>82946</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Finnboriset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>519461</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7034370</v>
-      </c>
-      <c r="S56" t="n">
-        <v>25</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>128047044</v>
-      </c>
-      <c r="B57" t="n">
-        <v>75175</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Finnboriset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>519462</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7034369</v>
-      </c>
-      <c r="S57" t="n">
-        <v>25</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55921-2023 artfynd.xlsx
+++ b/artfynd/A 55921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467565</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047087</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047095</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047030</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047034</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047062</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047044</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467553</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467554</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467555</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467556</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467557</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467558</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467559</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467560</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467561</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467562</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2707,6 +2807,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467564</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467566</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467567</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3013,6 +3128,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467568</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3115,6 +3235,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467570</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3217,6 +3342,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467571</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3319,6 +3449,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467572</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3421,6 +3556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467573</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3523,6 +3663,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467574</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3625,6 +3770,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467575</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3727,6 +3877,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467576</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3829,6 +3984,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467577</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3931,6 +4091,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467578</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4033,6 +4198,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467579</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4135,6 +4305,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467580</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4237,6 +4412,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467581</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4339,6 +4519,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467582</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4441,6 +4626,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467583</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4543,6 +4733,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467584</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4645,6 +4840,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467586</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4747,6 +4947,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467587</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4849,6 +5054,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467588</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4951,6 +5161,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467589</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5053,6 +5268,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467590</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5155,6 +5375,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467591</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5257,6 +5482,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467592</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5359,6 +5589,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467593</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5461,6 +5696,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467594</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5563,6 +5803,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467595</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5665,6 +5910,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467596</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5767,6 +6017,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467597</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5869,6 +6124,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467598</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5971,8 +6231,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>